--- a/data/trans_bre/P1803_2016_2023-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1803_2016_2023-Clase-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 4,41</t>
+          <t>-3,6; 4,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 7,92</t>
+          <t>-0,46; 7,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 80,58</t>
+          <t>-38,77; 78,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 71,49</t>
+          <t>-2,68; 76,03</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,59</t>
+          <t>1,51; 8,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 11,31</t>
+          <t>3,55; 11,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,61; 364,63</t>
+          <t>21,37; 339,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,44; 181,0</t>
+          <t>34,88; 193,05</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-33,72</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-78,52%</t>
+          <t>-10,93%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 7,47</t>
+          <t>-1,53; 7,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-69,17; 0,52</t>
+          <t>-5,56; 3,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 205,18</t>
+          <t>-31,35; 224,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-92,29; 4,83</t>
+          <t>-46,77; 46,97</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,04</t>
+          <t>-0,25; 3,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 5,0</t>
+          <t>0,86; 5,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 109,86</t>
+          <t>-6,49; 106,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 80,49</t>
+          <t>10,24; 101,36</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,06</t>
+          <t>-1,26; 2,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,79</t>
+          <t>-0,41; 4,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,12; 128,84</t>
+          <t>-29,36; 124,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 78,96</t>
+          <t>-5,78; 116,62</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-7,24%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,65</t>
+          <t>-2,75; 2,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 4,06</t>
+          <t>-6,14; 4,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,64; 149,41</t>
+          <t>-46,03; 169,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,96; 224,73</t>
+          <t>-54,35; 297,0</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-5,56</t>
+          <t>2,0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-36,8%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,14</t>
+          <t>-0,0; 2,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 1,65</t>
+          <t>0,53; 3,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 54,31</t>
+          <t>-0,05; 52,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-75,15; 19,53</t>
+          <t>5,88; 46,09</t>
         </is>
       </c>
     </row>
